--- a/更新範本的話請將檔案丟到本資料夾/生態調查資料填寫.xlsx
+++ b/更新範本的話請將檔案丟到本資料夾/生態調查資料填寫.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\FS01.eri.com.tw\第３組\環管署-OEIA\115\03.工作項目\05.優化監測數據上傳功能\2.環境監測欄位填寫表單-提供使用者版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D41177-6F5B-431F-92C5-27EF884A975C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED9ADE27-1A94-4627-B110-FB9DAD506984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="6720" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="監測點基本資料" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>日期(起)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -138,6 +138,10 @@
   <si>
     <t>備註</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>單位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -542,20 +546,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A1F5A00-3110-4170-B429-F5DBA55575A2}">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr defaultColWidth="47.875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="6" width="15.625" style="2" customWidth="1"/>
     <col min="7" max="8" width="23.625" style="2" customWidth="1"/>
     <col min="9" max="10" width="15.625" style="2" customWidth="1"/>
     <col min="11" max="11" width="23.625" style="2" customWidth="1"/>
-    <col min="12" max="16" width="15.625" style="2" customWidth="1"/>
-    <col min="17" max="19" width="23.625" style="2" customWidth="1"/>
-    <col min="20" max="20" width="15.625" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="47.875" style="2"/>
+    <col min="12" max="17" width="15.625" style="2" customWidth="1"/>
+    <col min="18" max="20" width="23.625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="15.625" style="2" customWidth="1"/>
+    <col min="22" max="16384" width="47.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -598,22 +602,25 @@
       <c r="N1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
